--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
@@ -519,7 +519,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:16:07.880Z</t>
+    <t>2026-10-11T16:44:58.508Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
@@ -519,7 +519,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T16:44:58.508Z</t>
+    <t>2026-10-11T17:07:27.789Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
@@ -519,7 +519,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-11T17:07:27.789Z</t>
+    <t>2026-10-12T01:35:49.292Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
@@ -519,7 +519,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T01:35:49.292Z</t>
+    <t>2026-10-12T02:10:48.801Z</t>
   </si>
   <si>
     <t>Column order</t>

--- a/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
+++ b/agentic-qe-mvp/demo-artifacts/flow-1-hotel-eqe-CYC-1/03-test-cases/CYC-1-test-cases.xlsx
@@ -519,7 +519,7 @@
     <t>Exported at</t>
   </si>
   <si>
-    <t>2026-10-12T02:10:48.801Z</t>
+    <t>2026-10-12T02:22:46.615Z</t>
   </si>
   <si>
     <t>Column order</t>
